--- a/yandex-kit-import.xlsx
+++ b/yandex-kit-import.xlsx
@@ -693,7 +693,7 @@
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>1782380055039</t>
+          <t>1782380506281</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
@@ -731,7 +731,11 @@
       <c r="Y2" t="inlineStr"/>
       <c r="Z2" t="inlineStr"/>
       <c r="AA2" t="inlineStr"/>
-      <c r="AB2" t="inlineStr"/>
+      <c r="AB2" t="inlineStr">
+        <is>
+          <t>https://techno-buyer.ru/wa-data/public/shop/products/78/17/1778/images/8986/8986.970.jpg https://techno-buyer.ru/wa-data/public/shop/products/78/17/1778/images/8987/8987.970.jpg https://techno-buyer.ru/wa-data/public/shop/products/78/17/1778/images/8988/8988.970.jpg https://techno-buyer.ru/wa-data/public/shop/products/78/17/1778/images/8989/8989.970.jpg</t>
+        </is>
+      </c>
       <c r="AC2" t="inlineStr"/>
       <c r="AD2" t="inlineStr"/>
       <c r="AE2" t="inlineStr"/>
@@ -844,7 +848,7 @@
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>1782380055039</t>
+          <t>1782380506281</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
@@ -882,7 +886,11 @@
       <c r="Y3" t="inlineStr"/>
       <c r="Z3" t="inlineStr"/>
       <c r="AA3" t="inlineStr"/>
-      <c r="AB3" t="inlineStr"/>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>https://techno-buyer.ru/wa-data/public/shop/products/85/15/1585/images/8512/8512.970.jpg https://techno-buyer.ru/wa-data/public/shop/products/85/15/1585/images/8513/8513.970.jpg https://techno-buyer.ru/wa-data/public/shop/products/85/15/1585/images/8514/8514.970.jpg https://techno-buyer.ru/wa-data/public/shop/products/85/15/1585/images/8515/8515.970.jpg</t>
+        </is>
+      </c>
       <c r="AC3" t="inlineStr"/>
       <c r="AD3" t="inlineStr"/>
       <c r="AE3" t="inlineStr"/>
@@ -995,7 +1003,7 @@
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>1782380055039</t>
+          <t>1782380506281</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
@@ -1033,7 +1041,11 @@
       <c r="Y4" t="inlineStr"/>
       <c r="Z4" t="inlineStr"/>
       <c r="AA4" t="inlineStr"/>
-      <c r="AB4" t="inlineStr"/>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>https://techno-buyer.ru/wa-data/public/shop/products/79/17/1779/images/8990/8990.970.jpg https://techno-buyer.ru/wa-data/public/shop/products/79/17/1779/images/8991/8991.970.jpg https://techno-buyer.ru/wa-data/public/shop/products/79/17/1779/images/8992/8992.970.jpg https://techno-buyer.ru/wa-data/public/shop/products/79/17/1779/images/8993/8993.970.jpg</t>
+        </is>
+      </c>
       <c r="AC4" t="inlineStr"/>
       <c r="AD4" t="inlineStr"/>
       <c r="AE4" t="inlineStr"/>
@@ -1146,7 +1158,7 @@
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>1782380055039</t>
+          <t>1782380506281</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
@@ -1184,7 +1196,11 @@
       <c r="Y5" t="inlineStr"/>
       <c r="Z5" t="inlineStr"/>
       <c r="AA5" t="inlineStr"/>
-      <c r="AB5" t="inlineStr"/>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>https://techno-buyer.ru/wa-data/public/shop/products/80/17/1780/images/8994/8994.970.jpg https://techno-buyer.ru/wa-data/public/shop/products/80/17/1780/images/8995/8995.970.jpg https://techno-buyer.ru/wa-data/public/shop/products/80/17/1780/images/8996/8996.970.jpg https://techno-buyer.ru/wa-data/public/shop/products/80/17/1780/images/8997/8997.970.jpg</t>
+        </is>
+      </c>
       <c r="AC5" t="inlineStr"/>
       <c r="AD5" t="inlineStr"/>
       <c r="AE5" t="inlineStr"/>
@@ -1297,7 +1313,7 @@
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>1782380055039</t>
+          <t>1782380506281</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
@@ -1335,7 +1351,11 @@
       <c r="Y6" t="inlineStr"/>
       <c r="Z6" t="inlineStr"/>
       <c r="AA6" t="inlineStr"/>
-      <c r="AB6" t="inlineStr"/>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>https://techno-buyer.ru/wa-data/public/shop/products/84/15/1584/images/8508/8508.970.jpg https://techno-buyer.ru/wa-data/public/shop/products/84/15/1584/images/8509/8509.970.jpg https://techno-buyer.ru/wa-data/public/shop/products/84/15/1584/images/8510/8510.970.jpg https://techno-buyer.ru/wa-data/public/shop/products/84/15/1584/images/8511/8511.970.jpg</t>
+        </is>
+      </c>
       <c r="AC6" t="inlineStr"/>
       <c r="AD6" t="inlineStr"/>
       <c r="AE6" t="inlineStr"/>
@@ -1448,7 +1468,7 @@
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>1782380055039</t>
+          <t>1782380506281</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
@@ -1486,7 +1506,11 @@
       <c r="Y7" t="inlineStr"/>
       <c r="Z7" t="inlineStr"/>
       <c r="AA7" t="inlineStr"/>
-      <c r="AB7" t="inlineStr"/>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>https://techno-buyer.ru/wa-data/public/shop/products/83/15/1583/images/8516/8516.970.jpg https://techno-buyer.ru/wa-data/public/shop/products/83/15/1583/images/8517/8517.970.jpg https://techno-buyer.ru/wa-data/public/shop/products/83/15/1583/images/8518/8518.970.jpg https://techno-buyer.ru/wa-data/public/shop/products/83/15/1583/images/8519/8519.970.jpg</t>
+        </is>
+      </c>
       <c r="AC7" t="inlineStr"/>
       <c r="AD7" t="inlineStr"/>
       <c r="AE7" t="inlineStr"/>
@@ -1599,7 +1623,7 @@
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>1782380055039</t>
+          <t>1782380506281</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
@@ -1637,7 +1661,11 @@
       <c r="Y8" t="inlineStr"/>
       <c r="Z8" t="inlineStr"/>
       <c r="AA8" t="inlineStr"/>
-      <c r="AB8" t="inlineStr"/>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>https://techno-buyer.ru/wa-data/public/shop/products/81/17/1781/images/8998/8998.970.jpg https://techno-buyer.ru/wa-data/public/shop/products/81/17/1781/images/8999/8999.970.jpg https://techno-buyer.ru/wa-data/public/shop/products/81/17/1781/images/9000/9000.970.jpg https://techno-buyer.ru/wa-data/public/shop/products/81/17/1781/images/9001/9001.970.jpg</t>
+        </is>
+      </c>
       <c r="AC8" t="inlineStr"/>
       <c r="AD8" t="inlineStr"/>
       <c r="AE8" t="inlineStr"/>
@@ -1750,7 +1778,7 @@
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>1782380055039</t>
+          <t>1782380506281</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
@@ -1788,7 +1816,11 @@
       <c r="Y9" t="inlineStr"/>
       <c r="Z9" t="inlineStr"/>
       <c r="AA9" t="inlineStr"/>
-      <c r="AB9" t="inlineStr"/>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>https://techno-buyer.ru/wa-data/public/shop/products/82/17/1782/images/9002/9002.970.jpg https://techno-buyer.ru/wa-data/public/shop/products/82/17/1782/images/9003/9003.970.jpg https://techno-buyer.ru/wa-data/public/shop/products/82/17/1782/images/9004/9004.970.jpg https://techno-buyer.ru/wa-data/public/shop/products/82/17/1782/images/9005/9005.970.jpg</t>
+        </is>
+      </c>
       <c r="AC9" t="inlineStr"/>
       <c r="AD9" t="inlineStr"/>
       <c r="AE9" t="inlineStr"/>
@@ -1901,7 +1933,7 @@
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>1782380055039</t>
+          <t>1782380506281</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
@@ -1939,7 +1971,11 @@
       <c r="Y10" t="inlineStr"/>
       <c r="Z10" t="inlineStr"/>
       <c r="AA10" t="inlineStr"/>
-      <c r="AB10" t="inlineStr"/>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>https://techno-buyer.ru/wa-data/public/shop/products/83/17/1783/images/9006/9006.970.jpg https://techno-buyer.ru/wa-data/public/shop/products/83/17/1783/images/9007/9007.970.jpg https://techno-buyer.ru/wa-data/public/shop/products/83/17/1783/images/9008/9008.970.jpg https://techno-buyer.ru/wa-data/public/shop/products/83/17/1783/images/9009/9009.970.jpg</t>
+        </is>
+      </c>
       <c r="AC10" t="inlineStr"/>
       <c r="AD10" t="inlineStr"/>
       <c r="AE10" t="inlineStr"/>
@@ -2052,7 +2088,7 @@
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>1782380055039</t>
+          <t>1782380506281</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
@@ -2090,7 +2126,11 @@
       <c r="Y11" t="inlineStr"/>
       <c r="Z11" t="inlineStr"/>
       <c r="AA11" t="inlineStr"/>
-      <c r="AB11" t="inlineStr"/>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>https://techno-buyer.ru/wa-data/public/shop/products/84/17/1784/images/9010/9010.970.jpg https://techno-buyer.ru/wa-data/public/shop/products/84/17/1784/images/9011/9011.970.jpg https://techno-buyer.ru/wa-data/public/shop/products/84/17/1784/images/9012/9012.970.jpg https://techno-buyer.ru/wa-data/public/shop/products/84/17/1784/images/9013/9013.970.jpg</t>
+        </is>
+      </c>
       <c r="AC11" t="inlineStr"/>
       <c r="AD11" t="inlineStr"/>
       <c r="AE11" t="inlineStr"/>
@@ -2203,7 +2243,7 @@
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>1782380055039</t>
+          <t>1782380506281</t>
         </is>
       </c>
       <c r="O12" t="inlineStr">
@@ -2241,7 +2281,11 @@
       <c r="Y12" t="inlineStr"/>
       <c r="Z12" t="inlineStr"/>
       <c r="AA12" t="inlineStr"/>
-      <c r="AB12" t="inlineStr"/>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>https://techno-buyer.ru/wa-data/public/shop/products/85/17/1785/images/9014/9014.970.jpg https://techno-buyer.ru/wa-data/public/shop/products/85/17/1785/images/9015/9015.970.jpg https://techno-buyer.ru/wa-data/public/shop/products/85/17/1785/images/9016/9016.970.jpg https://techno-buyer.ru/wa-data/public/shop/products/85/17/1785/images/9017/9017.970.jpg</t>
+        </is>
+      </c>
       <c r="AC12" t="inlineStr"/>
       <c r="AD12" t="inlineStr"/>
       <c r="AE12" t="inlineStr"/>
@@ -2354,7 +2398,7 @@
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>1782380055039</t>
+          <t>1782380506281</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
@@ -2392,7 +2436,11 @@
       <c r="Y13" t="inlineStr"/>
       <c r="Z13" t="inlineStr"/>
       <c r="AA13" t="inlineStr"/>
-      <c r="AB13" t="inlineStr"/>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>https://techno-buyer.ru/wa-data/public/shop/products/86/17/1786/images/9018/9018.970.jpg https://techno-buyer.ru/wa-data/public/shop/products/86/17/1786/images/9083/9083.970.jpg https://techno-buyer.ru/wa-data/public/shop/products/86/17/1786/images/9084/9084.970.jpg https://techno-buyer.ru/wa-data/public/shop/products/86/17/1786/images/9085/9085.970.jpg</t>
+        </is>
+      </c>
       <c r="AC13" t="inlineStr"/>
       <c r="AD13" t="inlineStr"/>
       <c r="AE13" t="inlineStr"/>
